--- a/agenda.xlsx
+++ b/agenda.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -859,39 +859,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>eduardo erika</t>
+          <t>patrick</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Corte e Barba</t>
+          <t>Corte</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>patrick</t>
+          <t xml:space="preserve">vitor e pai luzes </t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -903,44 +903,44 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">vitor e pai luzes </t>
+          <t>Ton mecanico</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Corte</t>
+          <t>Corte e Barba</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ton mecanico</t>
+          <t>Lene</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Corte e Barba</t>
+          <t>Corte</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lene</t>
+          <t>teste</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,29 +979,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Corte</t>
+          <t>Corte e Barba</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>pastor Daniel</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1013,7 +1013,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pastor Daniel</t>
+          <t>Fininho</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Corte e Barba</t>
+          <t>Corte</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Fininho</t>
+          <t>ninjinha</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1057,12 +1057,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ninjinha</t>
+          <t>anderson</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1079,17 +1079,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>anderson</t>
+          <t xml:space="preserve">eduardo erika </t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1101,17 +1101,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">eduardo erika </t>
+          <t>patrick</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1123,17 +1123,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>patrick</t>
+          <t xml:space="preserve">luzes pai e filho </t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1145,17 +1145,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">luzes pai e filho </t>
+          <t xml:space="preserve">ton </t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1167,95 +1167,95 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">ton </t>
+          <t xml:space="preserve">philype </t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Corte</t>
+          <t>cabelo e barba +5519998940637</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">philype </t>
+          <t xml:space="preserve">ronaldo </t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>cabelo e barba +5519998940637</t>
+          <t xml:space="preserve">corte e barba </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">ronaldo </t>
+          <t xml:space="preserve">Bruno Viana </t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte e barba </t>
+          <t xml:space="preserve">corte luzes sombracelha e barba </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bruno Viana </t>
+          <t xml:space="preserve">Marquinhos Rubia </t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte luzes sombracelha e barba </t>
+          <t xml:space="preserve">corte </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marquinhos Rubia </t>
+          <t xml:space="preserve">kauan Elaine </t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1277,17 +1277,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">kauan Elaine </t>
+          <t xml:space="preserve">filhos do marquinhos </t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">filhos do marquinhos </t>
+          <t>Antonio juma Lembi</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1309,24 +1309,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte </t>
+          <t xml:space="preserve">corte e barba </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Antonio juma Lembi</t>
+          <t xml:space="preserve">Robson </t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte e barba </t>
+          <t xml:space="preserve">corte luzes sombracelha e barba </t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1358,24 +1358,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte luzes sombracelha e barba </t>
+          <t xml:space="preserve">corte e barba </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robson </t>
+          <t xml:space="preserve">gui </t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1387,29 +1387,29 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">gui </t>
+          <t xml:space="preserve">Gui </t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte e barba </t>
+          <t xml:space="preserve">corte luzes sombracelha e barba </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gui </t>
+          <t>Lene</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte luzes sombracelha e barba </t>
+          <t>Corte + Sobrancelha</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Corte + Sobrancelha</t>
+          <t>Corte e Barba</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Lene</t>
+          <t>kkkk</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1507,19 +1507,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Corte e Barba</t>
+          <t>Corte + Sobrancelha</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kkkk</t>
+          <t>pastor Daniel</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>pastor Daniel</t>
+          <t>esdra</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1551,19 +1551,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Corte + Sobrancelha</t>
+          <t>Corte</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>esdra</t>
+          <t xml:space="preserve">costela  </t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1573,19 +1573,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Corte</t>
+          <t>Corte + Sobrancelha</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">costela  </t>
+          <t>esdra</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Corte + Sobrancelha</t>
+          <t>Corte</t>
         </is>
       </c>
     </row>
@@ -1622,51 +1622,51 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Corte</t>
+          <t>Corte + Sobrancelha</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>esdra</t>
+          <t>pretinho</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Corte + Sobrancelha</t>
+          <t xml:space="preserve">corte luzes sombracelha e barba </t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>pretinho</t>
+          <t xml:space="preserve">pretinho </t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte luzes sombracelha e barba </t>
+          <t xml:space="preserve">corte e barba </t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">pretinho </t>
+          <t>esdra</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1710,51 +1710,51 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte e barba </t>
+          <t xml:space="preserve">corte luzes sombracelha e barba </t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>esdra</t>
+          <t>darcy</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte luzes sombracelha e barba </t>
+          <t xml:space="preserve">corte </t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>darcy</t>
+          <t>Lene</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte </t>
+          <t xml:space="preserve">corte e barba </t>
         </is>
       </c>
     </row>
@@ -1837,46 +1837,46 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte e barba </t>
+          <t xml:space="preserve">corte luzes sombracelha e barba </t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Lene</t>
+          <t>darcy</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte luzes sombracelha e barba </t>
+          <t xml:space="preserve">corte </t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>darcy</t>
+          <t>Billy</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1893,12 +1893,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Billy</t>
+          <t>pastor Daniel</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1908,90 +1908,90 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte </t>
+          <t xml:space="preserve">corte e barba </t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>pastor Daniel</t>
+          <t xml:space="preserve">brow </t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte e barba </t>
+          <t>corte e barba e pigmentação</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">brow </t>
+          <t>gil</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>corte e barba e pigmentação</t>
+          <t xml:space="preserve">corte </t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>gil</t>
+          <t>luiz lorenço</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte </t>
+          <t>corte e sombracelha</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>luiz lorenço</t>
+          <t>Antonio juma Lembi</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Antonio juma Lembi</t>
+          <t>Ton mecanico</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2013,29 +2013,29 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>corte e sombracelha</t>
+          <t xml:space="preserve">corte e barba </t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ton mecanico</t>
+          <t>dioclesio</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2047,44 +2047,506 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>dioclesio</t>
+          <t>lilica</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte e barba </t>
+          <t xml:space="preserve">corte luzes </t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>lilica</t>
+          <t>shall</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>shall</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>esdra</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>esdra</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>esdra</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Corte</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Corte e Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Corte + Sobrancelha</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Corte e Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>esdra</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Corte</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paulo </t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paulo </t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paulo </t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Corte e Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>dj dennyboy</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
           <t>2025-12-23</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">corte luzes </t>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>josi</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Corte e Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Corte e Barba</t>
         </is>
       </c>
     </row>

--- a/agenda.xlsx
+++ b/agenda.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1695,44 +1695,44 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>esdra</t>
+          <t>darcy</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte luzes sombracelha e barba </t>
+          <t xml:space="preserve">corte </t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>darcy</t>
+          <t>Lene</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte </t>
+          <t xml:space="preserve">corte e barba </t>
         </is>
       </c>
     </row>
@@ -1815,46 +1815,46 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte e barba </t>
+          <t xml:space="preserve">corte luzes sombracelha e barba </t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lene</t>
+          <t>darcy</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte luzes sombracelha e barba </t>
+          <t xml:space="preserve">corte </t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>darcy</t>
+          <t>Billy</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1871,12 +1871,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Billy</t>
+          <t>pastor Daniel</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1886,90 +1886,90 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte </t>
+          <t xml:space="preserve">corte e barba </t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>pastor Daniel</t>
+          <t xml:space="preserve">brow </t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte e barba </t>
+          <t>corte e barba e pigmentação</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">brow </t>
+          <t>gil</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>corte e barba e pigmentação</t>
+          <t xml:space="preserve">corte </t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>gil</t>
+          <t>luiz lorenço</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte </t>
+          <t>corte e sombracelha</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>luiz lorenço</t>
+          <t>Antonio juma Lembi</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Antonio juma Lembi</t>
+          <t>Ton mecanico</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1991,29 +1991,29 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>corte e sombracelha</t>
+          <t xml:space="preserve">corte e barba </t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ton mecanico</t>
+          <t>dioclesio</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2025,51 +2025,51 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>dioclesio</t>
+          <t>lilica</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte e barba </t>
+          <t xml:space="preserve">corte luzes </t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>lilica</t>
+          <t>shall</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte luzes </t>
+          <t>Barba</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>shall</t>
+          <t>Lene</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2091,7 +2091,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Lene</t>
+          <t>shall</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2113,7 +2113,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>shall</t>
+          <t>Lene</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2135,7 +2135,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Lene</t>
+          <t>esdra</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2179,7 +2179,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>esdra</t>
+          <t>Lene</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Lene</t>
+          <t>esdra</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2223,7 +2223,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>esdra</t>
+          <t>Lene</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Barba</t>
+          <t>Corte</t>
         </is>
       </c>
     </row>
@@ -2255,12 +2255,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Corte</t>
+          <t>Corte e Barba</t>
         </is>
       </c>
     </row>
@@ -2277,12 +2277,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Corte e Barba</t>
+          <t>Barba</t>
         </is>
       </c>
     </row>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Barba</t>
+          <t>Corte + Sobrancelha</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Corte + Sobrancelha</t>
+          <t>Barba</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Barba</t>
+          <t>Corte e Barba</t>
         </is>
       </c>
     </row>
@@ -2365,19 +2365,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Corte e Barba</t>
+          <t>Barba</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Lene</t>
+          <t>esdra</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2387,34 +2387,34 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Barba</t>
+          <t>Corte</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>esdra</t>
+          <t xml:space="preserve">Paulo </t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Corte</t>
+          <t xml:space="preserve">corte e barba </t>
         </is>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paulo </t>
+          <t xml:space="preserve">paulo </t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2458,68 +2458,68 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte e barba </t>
+          <t>Corte e Barba</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">paulo </t>
+          <t>dj dennyboy</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Corte e Barba</t>
+          <t xml:space="preserve">corte e barba </t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>dj dennyboy</t>
+          <t>Lene</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">corte e barba </t>
+          <t>Corte e Barba</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>josi</t>
+          <t xml:space="preserve">juninho </t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2536,17 +2536,743 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>esdra</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Corte e Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Billy</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte </t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
           <t>2025-12-30</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Corte e Barba</t>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>marquito</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brow </t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>kevin</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte </t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>claudinho</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte </t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ronaldo </t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corte e barba </t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Corte</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>shall</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Corte</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>liiiii</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Corte</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>liiiii</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>esdra</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Barba</t>
         </is>
       </c>
     </row>

--- a/agenda.xlsx
+++ b/agenda.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D130"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3276,6 +3276,94 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>esdra</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Lene</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Corte + Sobrancelha</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
